--- a/OUTPUT/direct_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
+++ b/OUTPUT/direct_P23836_Escherichia_coli_str__K-12_substr__MG1655.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.002</v>
+        <v>0.002199120351859256</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.3516</v>
+        <v>0.3516593362654938</v>
       </c>
     </row>
   </sheetData>
